--- a/public/files/GuidesTemplate.xlsx
+++ b/public/files/GuidesTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Admin-Multientrega-v2\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F2E3B60-D9D0-4A84-81D2-E4BDD7B69C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DFA4750-81D1-4377-990C-E7A7FB68D7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{ED1948C0-61BA-41CD-B353-EFF3FE089133}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{307E6105-2057-4EB5-9090-6577891F49CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>ClaseOrden</t>
   </si>
@@ -43,7 +43,7 @@
     <t>TipoDocumento</t>
   </si>
   <si>
-    <t>OrdenID</t>
+    <t>OrdeID</t>
   </si>
   <si>
     <t>Item</t>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>FechaProgramada</t>
+  </si>
+  <si>
+    <t>EmailDeContacto</t>
+  </si>
+  <si>
+    <t>TelefonoDeContacto</t>
   </si>
 </sst>
 </file>
@@ -427,11 +433,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DA9A18-F77F-4B16-B033-C484350AA6F1}">
-  <dimension ref="A1:N1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B59F17-9F5C-4C23-B800-B7401824C5BD}">
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,6 +496,12 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
